--- a/data/trans_bre/IP21-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 6,07</t>
+          <t>-3,17; 6,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,83</t>
+          <t>-4,3; 1,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,08</t>
+          <t>-2,61; 4,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,94</t>
+          <t>-2,74; 2,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,66; 290,52</t>
+          <t>-58,13; 390,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 652,8</t>
+          <t>-100,0; 488,91</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 7,93</t>
+          <t>-2,25; 7,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,72</t>
+          <t>-5,24; 2,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,4</t>
+          <t>-4,63; 2,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 6,06</t>
+          <t>-0,19; 5,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,64; 552,42</t>
+          <t>-48,87; 643,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 272,36</t>
+          <t>-82,07; 194,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -0,94</t>
+          <t>-9,24; -0,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 1,76</t>
+          <t>-7,06; 1,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,22</t>
+          <t>-7,61; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,45</t>
+          <t>-2,03; 4,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,81</t>
+          <t>-100,0; 36,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 165,51</t>
+          <t>-100,0; 112,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,94</t>
+          <t>-90,11; 239,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,89</t>
+          <t>-4,63; 2,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,14</t>
+          <t>-1,69; 6,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,03</t>
+          <t>-2,29; 2,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,33</t>
+          <t>-4,35; 0,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 65,92</t>
+          <t>-69,05; 85,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 189,66</t>
+          <t>-27,93; 216,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,11; 256,55</t>
+          <t>-76,47; 296,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,72</t>
+          <t>-100,0; 81,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,98</t>
+          <t>-4,1; 3,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 1,88</t>
+          <t>-5,83; 2,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,17</t>
+          <t>-4,19; 3,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,04</t>
+          <t>-2,26; 3,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-82,32; 177,44</t>
+          <t>-80,41; 206,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-78,73; 87,49</t>
+          <t>-78,83; 94,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,44; 256,68</t>
+          <t>-68,08; 207,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 512,74</t>
+          <t>-100,0; 793,0</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 1,78</t>
+          <t>-8,71; 1,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 2,2</t>
+          <t>-9,76; 2,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 8,98</t>
+          <t>-0,05; 9,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 0,0</t>
+          <t>-5,63; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,75</t>
+          <t>-100,0; 127,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,73</t>
+          <t>-100,0; 152,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,89</t>
+          <t>-2,43; 0,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,16</t>
+          <t>-2,25; 1,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,38</t>
+          <t>-1,51; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,74</t>
+          <t>-1,51; 0,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-47,96; 24,13</t>
+          <t>-45,92; 23,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 32,28</t>
+          <t>-42,73; 31,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-41,58; 62,19</t>
+          <t>-42,91; 60,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-63,19; 73,9</t>
+          <t>-65,14; 74,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 6,06</t>
+          <t>-3,66; 5,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,81</t>
+          <t>-4,46; 1,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,72</t>
+          <t>-2,46; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,92</t>
+          <t>-2,88; 2,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,13; 390,41</t>
+          <t>-63,1; 287,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 488,91</t>
+          <t>-100,0; 490,47</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,96</t>
+          <t>-2,43; 7,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,8</t>
+          <t>-4,75; 2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,92</t>
+          <t>-4,29; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,8</t>
+          <t>-0,26; 5,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 643,33</t>
+          <t>-55,18; 626,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 437,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,07; 194,99</t>
+          <t>-78,03; 247,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -0,91</t>
+          <t>-9,17; -0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1,57</t>
+          <t>-7,26; 1,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,7</t>
+          <t>-8,02; 2,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,16</t>
+          <t>-2,05; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,57</t>
+          <t>-100,0; 37,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 112,3</t>
+          <t>-100,0; 200,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-90,11; 239,18</t>
+          <t>-100,0; 184,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,02</t>
+          <t>-4,56; 1,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 6,37</t>
+          <t>-1,38; 6,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,33</t>
+          <t>-2,17; 2,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,28</t>
+          <t>-4,38; 0,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,05; 85,79</t>
+          <t>-68,58; 59,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 216,21</t>
+          <t>-25,74; 203,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,47; 296,36</t>
+          <t>-73,66; 309,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 81,17</t>
+          <t>-100,0; 101,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,25</t>
+          <t>-4,32; 3,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 2,11</t>
+          <t>-5,76; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 3,88</t>
+          <t>-4,01; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,15</t>
+          <t>-2,45; 2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 206,96</t>
+          <t>-79,53; 225,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-78,83; 94,86</t>
+          <t>-78,32; 99,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 207,99</t>
+          <t>-65,21; 237,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 793,0</t>
+          <t>-100,0; 418,42</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 1,66</t>
+          <t>-9,01; 1,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 2,16</t>
+          <t>-9,61; 1,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 9,19</t>
+          <t>-0,1; 8,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,0</t>
+          <t>-5,87; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,84</t>
+          <t>-100,0; 92,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,76</t>
+          <t>-100,0; 98,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,88</t>
+          <t>-2,7; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,12</t>
+          <t>-2,29; 1,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,32</t>
+          <t>-1,46; 1,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,74</t>
+          <t>-1,4; 0,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,92; 23,99</t>
+          <t>-48,76; 22,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 31,9</t>
+          <t>-43,0; 36,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 60,41</t>
+          <t>-40,14; 59,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 74,15</t>
+          <t>-60,53; 80,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 5,77</t>
+          <t>-3,13; 6,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,75</t>
+          <t>-4,79; 1,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 4,03</t>
+          <t>-2,52; 4,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,96</t>
+          <t>-2,53; 3,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,1; 287,66</t>
+          <t>-57,66; 290,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 490,47</t>
+          <t>-100,0; 775,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>312,54%</t>
+          <t>273,27%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 7,69</t>
+          <t>-2,87; 7,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,79</t>
+          <t>-4,68; 2,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,08</t>
+          <t>-4,82; 3,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,82</t>
+          <t>-0,36; 5,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 626,58</t>
+          <t>-63,64; 552,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 437,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,03; 247,18</t>
+          <t>-83,19; 272,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -0,68</t>
+          <t>-9,33; -0,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 1,82</t>
+          <t>-6,91; 1,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 2,48</t>
+          <t>-7,91; 2,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,63</t>
+          <t>-1,77; 4,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,39</t>
+          <t>-100,0; 50,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 200,92</t>
+          <t>-100,0; 165,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 184,43</t>
+          <t>-100,0; 178,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-1,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-64,22%</t>
+          <t>-62,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,83</t>
+          <t>-4,69; 1,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,38</t>
+          <t>-1,52; 6,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,53</t>
+          <t>-2,26; 2,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,33</t>
+          <t>-4,29; 0,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,58; 59,28</t>
+          <t>-68,82; 65,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 203,23</t>
+          <t>-25,94; 189,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 309,42</t>
+          <t>-73,11; 256,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 101,94</t>
+          <t>-100,0; 90,48</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,53</t>
+          <t>-4,47; 2,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,88</t>
+          <t>-5,59; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,15</t>
+          <t>-3,62; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,86</t>
+          <t>-2,33; 3,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-79,53; 225,61</t>
+          <t>-82,32; 177,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-78,32; 99,08</t>
+          <t>-78,73; 87,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 237,82</t>
+          <t>-63,44; 256,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 418,42</t>
+          <t>-100,0; 526,91</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 1,54</t>
+          <t>-9,0; 1,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 1,84</t>
+          <t>-10,07; 2,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 8,67</t>
+          <t>-0,06; 8,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,0</t>
+          <t>-7,95; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,88</t>
+          <t>-100,0; 110,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,46</t>
+          <t>-100,0; 149,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-15,66%</t>
+          <t>-13,32%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,73</t>
+          <t>-2,66; 0,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,25</t>
+          <t>-2,3; 1,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,31</t>
+          <t>-1,54; 1,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,84</t>
+          <t>-1,51; 0,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 22,69</t>
+          <t>-47,96; 24,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 36,89</t>
+          <t>-44,39; 32,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 59,4</t>
+          <t>-41,58; 62,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 80,22</t>
+          <t>-63,74; 83,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-42,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.199962371015857</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.9302441534650142</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5014372708191599</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.07669689579239899</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2946968200017995</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4206078579406411</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2733499483542747</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.04424133125146895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,13; 6,07</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,79; 1,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 4,08</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,53; 3,23</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-57,66; 290,52</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 775,56</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.125158991254996</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.786527532542937</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.51724660625519</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.530548237994342</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5765882837329913</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.06699515042839</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.833007048663338</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.079874056142675</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.226859802548422</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.905161175390938</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>7.755614848826798</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>76,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-28,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-17,65%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>273,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 7,93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 2,72</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,82; 3,4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 5,7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-63,64; 552,42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-83,19; 272,36</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.577601780655661</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.8507984575026537</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6349060159106662</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.871356489986207</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.7679761985292207</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2864368384384172</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1764540774529871</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>2.73269553321086</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-4,61</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-83,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-49,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-48,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>65,01%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.873350732394453</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.682450169542729</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.818680324533518</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-0.3598068221655309</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6363553089397916</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="n">
+        <v>-0.8318773687217451</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,33; -0,94</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,91; 1,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,91; 2,22</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,77; 4,28</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 50,81</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 165,51</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 178,94</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.934970423611396</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.718852605322604</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.398862844488652</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.703553915886779</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>5.524201105090228</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="n">
+        <v>2.723561225974126</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +803,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,28</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-28,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-6,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-62,69%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-4.607246556546134</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.31451155131974</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.575982599089993</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.5718488838010871</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.8319654861630382</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4941774890799087</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4816174048878403</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.6500875820758113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,69; 1,89</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,52; 6,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 2,03</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,29; 0,4</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-68,82; 65,92</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-25,94; 189,66</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-73,11; 256,55</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 90,48</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.325841539481917</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.906974878722709</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.914872137078791</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.767450714572578</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.9384229205518304</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.761010632940746</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.224049363468355</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.278244349914904</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.5081344623177598</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.655103462598573</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.789397663469459</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-19,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-34,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-4,47; 2,98</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,59; 1,88</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 4,17</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,33; 3,03</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-82,32; 177,44</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-78,73; 87,49</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-63,44; 256,68</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 526,91</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.396671030383795</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.279487614559836</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.1394179269821372</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.441118039057632</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.282117691045676</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.4771180433326618</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.06726560893756268</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.6269052715692655</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-3,79</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-53,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-59,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>335,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.694005232049665</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.521443974079004</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.259491213214453</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.287557689801489</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6882403365189543</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2594197943530212</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7310853550576986</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-9,0; 1,78</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-10,07; 2,2</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-0,06; 8,98</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,95; 0,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 110,75</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 149,73</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.887337818232936</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.136443438797488</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.034791660826063</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.3977826639729933</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6591683897296335</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.896579658329684</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.565481253723305</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.9048013345019515</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +999,289 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-19,07%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-13,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-1,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-13,32%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.7263530527478607</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.674914822511644</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1079162655583603</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1389005640389168</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1943864559166183</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3420387635817306</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.02675400751460641</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.08115314712756103</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 0,89</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,3; 1,16</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,54; 1,38</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 0,79</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-47,96; 24,13</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-44,39; 32,28</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-41,58; 62,19</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-63,74; 83,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.473104014996894</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.587308568155831</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.617046374051079</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.325264134920312</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8231927039445704</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7872746138901043</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6343648686613851</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.978697641097847</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.878712296284114</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.170035653817925</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.03025666322278</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.774399137696859</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.8748652306385665</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.566757099925381</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>5.2690698572604</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-2.991500937887989</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-3.790378474517996</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>3.131220891986133</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.308069584615069</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.5312465967591427</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5971587292854774</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>3.352281245743272</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-9.003158189742084</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-10.06520930141352</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-0.06305951061937827</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.949485072765492</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1.779350661295378</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2.200739772039645</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>8.97527414373482</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.107524378757445</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.497321423854544</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.8690322481820695</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.5712314234682415</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.05013268365866956</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.2188223785176248</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1907171642751589</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.1301729434653037</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.01719119926570361</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.1332093807522554</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.65738479666746</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.300564858002041</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.544288456467761</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.511938927828109</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.4795523241816968</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4438733576184808</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.4157651521831596</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.637374940968513</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.888893950975794</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.16158947660001</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.384136520328759</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.7927800589707299</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.241346457825398</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.3227854434998558</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.6219121995910677</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.8388673165662871</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1289,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
